--- a/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 38,8</t>
+          <t>4,35; 38,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 13,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,02</t>
+          <t>0,0; 24,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,16</t>
+          <t>0,0; 16,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 25,22</t>
+          <t>4,59; 26,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,56</t>
+          <t>0,0; 11,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 22,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,55</t>
+          <t>0,0; 12,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,01</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,39</t>
+          <t>0,0; 20,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,89</t>
+          <t>1,67; 13,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,14</t>
+          <t>0,88; 8,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,93</t>
+          <t>0,0; 20,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 20,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,15</t>
+          <t>1,55; 14,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,51</t>
+          <t>0,87; 8,43</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 29,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,03</t>
+          <t>0,0; 31,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,57</t>
+          <t>0,0; 16,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,49</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 14,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,7</t>
+          <t>0,0; 15,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 11,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,2</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,86</t>
+          <t>0,0; 15,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,7</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,49</t>
+          <t>2,76; 9,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,07</t>
+          <t>0,6; 4,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,34; 2,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,52</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,6</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,3</t>
+          <t>0,44; 3,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,59</t>
+          <t>2,03; 5,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,44</t>
+          <t>0,97; 3,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,56</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2822</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>507; 4502</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2641</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2961</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3942</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1091; 6235</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4862</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1879</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3737</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4089</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2507</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4878</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>611; 4981</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>611; 5581</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4495</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3322</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2849</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>507; 4829</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>559; 5437</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4043</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4271</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3889</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3708</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4907</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3187</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4106</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3257</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4200</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 6354</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3157</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4025</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2961</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3227</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3768</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4020</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3459; 11637</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1123; 7525</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>558; 4656</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>669; 6158</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1875; 8700</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>659; 5451</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5470; 14693</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>3667; 13254</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 38,58</t>
+          <t>4,45; 38,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,86</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,4</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,03</t>
+          <t>0,0; 15,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 26,19</t>
+          <t>4,3; 24,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,14</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,34</t>
+          <t>0,0; 22,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,41</t>
+          <t>0,0; 11,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 15,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,92</t>
+          <t>0,0; 18,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,62</t>
+          <t>1,65; 13,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,02</t>
+          <t>0,86; 6,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,1</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,1</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,22</t>
+          <t>0,0; 17,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,73</t>
+          <t>1,57; 13,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,43</t>
+          <t>0,85; 7,94</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,75</t>
+          <t>0,0; 29,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>0,0; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,41</t>
+          <t>0,0; 24,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,05</t>
+          <t>0,0; 10,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>0,0; 15,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,64</t>
+          <t>0,0; 13,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 15,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,48</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,16</t>
+          <t>0,0; 11,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,53</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 12,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,29</t>
+          <t>2,85; 8,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,02</t>
+          <t>0,64; 3,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,86</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,47; 4,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>0,69; 4,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,68</t>
+          <t>0,44; 3,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,46</t>
+          <t>2,13; 5,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,51</t>
+          <t>1,01; 3,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,56</t>
+          <t>0,45; 2,53</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>507; 4502</t>
+          <t>519; 4519</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2641</t>
+          <t>0; 2696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2961</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1091; 6235</t>
+          <t>1023; 5814</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4862</t>
+          <t>0; 4638</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4089</t>
+          <t>0; 3886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2636</t>
+          <t>0; 2993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2507</t>
+          <t>0; 3155</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4878</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>611; 4981</t>
+          <t>602; 4987</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>611; 5581</t>
+          <t>596; 4848</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4495</t>
+          <t>0; 4868</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 3680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4924</t>
+          <t>0; 3654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3322</t>
+          <t>0; 2826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2849</t>
+          <t>0; 3271</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>507; 4829</t>
+          <t>514; 4470</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>559; 5437</t>
+          <t>550; 5125</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4271</t>
+          <t>0; 4031</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3889</t>
+          <t>0; 3069</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3708</t>
+          <t>0; 2501</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3315</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 3489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4591</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 6354</t>
+          <t>0; 5459</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 3065</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4025</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2961</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3227</t>
+          <t>0; 3262</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4020</t>
+          <t>0; 4633</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3459; 11637</t>
+          <t>3573; 11072</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1123; 7525</t>
+          <t>1193; 7245</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>558; 4656</t>
+          <t>557; 4794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>669; 6158</t>
+          <t>683; 6916</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1875; 8700</t>
+          <t>1314; 8057</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>659; 5451</t>
+          <t>656; 5618</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5470; 14693</t>
+          <t>5721; 14906</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3667; 13254</t>
+          <t>3803; 13004</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1349; 7953</t>
+          <t>1393; 7846</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>18,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 38,73</t>
+          <t>0,0; 29,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,15</t>
+          <t>0,0; 18,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,15</t>
+          <t>4,36; 38,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,72</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 24,43</t>
+          <t>4,4; 25,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 12,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,09</t>
+          <t>0,0; 17,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,79</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,07</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 13,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,63</t>
+          <t>1,67; 13,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,96</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,19</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,47</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,21</t>
+          <t>0,0; 20,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 10,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,64</t>
+          <t>1,57; 14,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,94</t>
+          <t>0,87; 7,51</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,07</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,01%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,82</t>
+          <t>0,0; 13,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,42</t>
+          <t>0,0; 13,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,71</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 14,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,06</t>
+          <t>0,0; 16,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
     </row>
@@ -1395,27 +1395,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,84</t>
+          <t>0,46; 4,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,87</t>
+          <t>0,81; 4,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,95</t>
+          <t>0,45; 3,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,81</t>
+          <t>3,04; 9,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,65; 4,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,79</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,54</t>
+          <t>2,13; 5,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,44</t>
+          <t>1,04; 3,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,53</t>
+          <t>0,45; 2,56</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2137</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>498</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>519; 4519</t>
+          <t>0; 3522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>0; 4465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>508; 4527</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 2424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1023; 5814</t>
+          <t>1046; 6003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4638</t>
+          <t>0; 5480</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 3063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2993</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3155</t>
+          <t>0; 4466</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>602; 4987</t>
+          <t>610; 5082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>596; 4848</t>
+          <t>0; 4970</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4868</t>
+          <t>0; 4398</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1149</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3680</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2826</t>
+          <t>0; 3422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 3730</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>514; 4470</t>
+          <t>514; 4638</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>550; 5125</t>
+          <t>561; 4846</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 4009</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2623,22 +2623,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>620</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2501</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 3236</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3102</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 5423</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3089</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4898</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5459</t>
+          <t>0; 5147</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>0; 3511</t>
         </is>
       </c>
     </row>
@@ -2896,22 +2896,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2949,27 +2949,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1102</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>582</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3486</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3228</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>0; 2606</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>0; 3820</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4633</t>
+          <t>0; 3857</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1762</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3573; 11072</t>
+          <t>669; 6504</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1193; 7245</t>
+          <t>1547; 8784</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557; 4794</t>
+          <t>661; 4881</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>683; 6916</t>
+          <t>3809; 11888</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1314; 8057</t>
+          <t>1211; 7613</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>656; 5618</t>
+          <t>554; 4830</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5721; 14906</t>
+          <t>5723; 15037</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3803; 13004</t>
+          <t>3915; 12980</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1393; 7846</t>
+          <t>1392; 7948</t>
         </is>
       </c>
     </row>
